--- a/roster.xlsx
+++ b/roster.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Repo\mentoring\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D467207-1BF8-4C41-942D-3B842B9223F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23979E1A-9A76-4AD3-AF0E-971B4A7665A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25180" windowHeight="16140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4080" yWindow="1910" windowWidth="18720" windowHeight="11690" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="18">
   <si>
     <t>last_name</t>
   </si>
@@ -36,9 +36,6 @@
     <t>year_start</t>
   </si>
   <si>
-    <t>year_graduate</t>
-  </si>
-  <si>
     <t>Charlotte</t>
   </si>
   <si>
@@ -67,6 +64,21 @@
   </si>
   <si>
     <t>Jimenez</t>
+  </si>
+  <si>
+    <t>Anand</t>
+  </si>
+  <si>
+    <t>Ebert</t>
+  </si>
+  <si>
+    <t>Belinky</t>
+  </si>
+  <si>
+    <t>RJ</t>
+  </si>
+  <si>
+    <t>Talia</t>
   </si>
 </sst>
 </file>
@@ -384,13 +396,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="13" width="12.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -400,72 +412,93 @@
       <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+      <c r="B2" t="s">
         <v>4</v>
-      </c>
-      <c r="B2" t="s">
-        <v>5</v>
       </c>
       <c r="C2">
         <v>2023</v>
       </c>
-      <c r="D2">
-        <v>2024</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" t="s">
         <v>6</v>
-      </c>
-      <c r="B3" t="s">
-        <v>7</v>
       </c>
       <c r="C3">
         <v>2023</v>
       </c>
-      <c r="D3">
-        <v>2025</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" t="s">
         <v>8</v>
-      </c>
-      <c r="B4" t="s">
-        <v>9</v>
       </c>
       <c r="C4">
         <v>2024</v>
       </c>
-      <c r="D4">
-        <v>2025</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" t="s">
         <v>10</v>
-      </c>
-      <c r="B5" t="s">
-        <v>11</v>
       </c>
       <c r="C5">
         <v>2025</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" t="s">
         <v>12</v>
-      </c>
-      <c r="B6" t="s">
-        <v>13</v>
       </c>
       <c r="C6">
         <v>2025</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C7">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C8">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>17</v>
+      </c>
+      <c r="B9" t="s">
+        <v>15</v>
+      </c>
+      <c r="C9">
+        <v>2026</v>
       </c>
     </row>
   </sheetData>
